--- a/dataset/Faulty/data_underflow.xlsx
+++ b/dataset/Faulty/data_underflow.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -632,14 +632,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -676,14 +676,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/data_underflow.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/data_underflow.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
